--- a/salidas/empresas/KMB.xlsx
+++ b/salidas/empresas/KMB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>26.16889190673828</v>
+        <v>26.16888618469238</v>
       </c>
       <c r="C2" t="n">
         <v>54.76510238647461</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>27.11264419555664</v>
+        <v>27.11264801025391</v>
       </c>
       <c r="C3" t="n">
         <v>56.74017333984375</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>26.70279693603516</v>
+        <v>26.70279884338379</v>
       </c>
       <c r="C4" t="n">
         <v>55.41706466674805</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>27.04004859924316</v>
+        <v>27.0400333404541</v>
       </c>
       <c r="C5" t="n">
         <v>56.11697006225586</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>28.0286922454834</v>
+        <v>28.0286865234375</v>
       </c>
       <c r="C6" t="n">
         <v>58.16874313354492</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>28.73845291137695</v>
+        <v>28.73846244812012</v>
       </c>
       <c r="C7" t="n">
         <v>59.15628051757812</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>28.43571472167969</v>
+        <v>28.43570899963379</v>
       </c>
       <c r="C8" t="n">
         <v>58.53307723999023</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>29.57686042785645</v>
+        <v>29.57685089111328</v>
       </c>
       <c r="C9" t="n">
         <v>60.88207244873047</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>30.67730712890625</v>
+        <v>30.67729949951172</v>
       </c>
       <c r="C10" t="n">
         <v>62.66538619995117</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>31.22175407409668</v>
+        <v>31.22177696228027</v>
       </c>
       <c r="C11" t="n">
         <v>63.77756500244141</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>31.19828796386719</v>
+        <v>31.19830131530762</v>
       </c>
       <c r="C12" t="n">
         <v>63.7296257019043</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>32.12498092651367</v>
+        <v>32.12498474121094</v>
       </c>
       <c r="C13" t="n">
         <v>65.14861297607422</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>32.81051254272461</v>
+        <v>32.81050109863281</v>
       </c>
       <c r="C14" t="n">
         <v>66.53883361816406</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>32.14861297607422</v>
+        <v>32.14861679077148</v>
       </c>
       <c r="C15" t="n">
         <v>65.19654846191406</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>32.63457107543945</v>
+        <v>32.63455581665039</v>
       </c>
       <c r="C16" t="n">
         <v>65.66634368896484</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>33.81148147583008</v>
+        <v>33.81149291992188</v>
       </c>
       <c r="C18" t="n">
         <v>68.03451538085938</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>32.10860443115234</v>
+        <v>32.10860824584961</v>
       </c>
       <c r="C19" t="n">
         <v>64.13230895996094</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>32.2910041809082</v>
+        <v>32.291015625</v>
       </c>
       <c r="C20" t="n">
         <v>64.49664306640625</v>
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>33.98677062988281</v>
+        <v>33.98675537109375</v>
       </c>
       <c r="C22" t="n">
         <v>67.36337280273438</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>34.29151916503906</v>
+        <v>34.29150772094727</v>
       </c>
       <c r="C23" t="n">
         <v>67.96739959716797</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>33.76908874511719</v>
+        <v>33.76910400390625</v>
       </c>
       <c r="C24" t="n">
         <v>66.93193054199219</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>33.80345916748047</v>
+        <v>33.80347442626953</v>
       </c>
       <c r="C25" t="n">
         <v>66.48130035400391</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>31.99484443664551</v>
+        <v>31.99483489990234</v>
       </c>
       <c r="C26" t="n">
         <v>62.92425537109375</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>31.77545547485352</v>
+        <v>31.77546501159668</v>
       </c>
       <c r="C27" t="n">
         <v>62.4928092956543</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>31.75169563293457</v>
+        <v>31.75168800354004</v>
       </c>
       <c r="C28" t="n">
         <v>61.8887825012207</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>31.47622871398926</v>
+        <v>31.47623443603516</v>
       </c>
       <c r="C29" t="n">
         <v>61.35187149047852</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>31.38278579711914</v>
+        <v>31.38276290893555</v>
       </c>
       <c r="C30" t="n">
         <v>61.16970443725586</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>29.67824935913086</v>
+        <v>29.67824363708496</v>
       </c>
       <c r="C31" t="n">
         <v>57.31543731689453</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>28.71015167236328</v>
+        <v>28.71015739440918</v>
       </c>
       <c r="C32" t="n">
         <v>55.44582748413086</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>30.62150764465332</v>
+        <v>30.62151718139648</v>
       </c>
       <c r="C33" t="n">
         <v>59.13710403442383</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>32.49001312255859</v>
+        <v>32.49001693725586</v>
       </c>
       <c r="C34" t="n">
         <v>62.16682434082031</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>30.71118354797363</v>
+        <v>30.711181640625</v>
       </c>
       <c r="C35" t="n">
         <v>58.76318359375</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>28.95740509033203</v>
+        <v>28.95740127563477</v>
       </c>
       <c r="C36" t="n">
         <v>55.40747833251953</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>26.69799423217773</v>
+        <v>26.69798469543457</v>
       </c>
       <c r="C37" t="n">
         <v>50.56567764282227</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>26.05509757995605</v>
+        <v>26.05510139465332</v>
       </c>
       <c r="C38" t="n">
         <v>49.3480339050293</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>23.84798431396484</v>
+        <v>23.84798049926758</v>
       </c>
       <c r="C39" t="n">
         <v>45.16778564453125</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>23.64956283569336</v>
+        <v>23.64955520629883</v>
       </c>
       <c r="C40" t="n">
         <v>44.20901107788086</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>25.20363426208496</v>
+        <v>25.20363616943359</v>
       </c>
       <c r="C41" t="n">
         <v>47.11409378051758</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>26.61409378051758</v>
+        <v>26.61410331726074</v>
       </c>
       <c r="C42" t="n">
         <v>49.75071716308594</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>27.19383811950684</v>
+        <v>27.19382858276367</v>
       </c>
       <c r="C43" t="n">
         <v>50.26845550537109</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>30.31621932983398</v>
+        <v>30.31621551513672</v>
       </c>
       <c r="C44" t="n">
         <v>56.04026794433594</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>31.35874557495117</v>
+        <v>31.35874366760254</v>
       </c>
       <c r="C45" t="n">
         <v>57.96740341186523</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>30.90486526489258</v>
+        <v>30.90486335754395</v>
       </c>
       <c r="C46" t="n">
         <v>56.54841613769531</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>32.04715347290039</v>
+        <v>32.04716491699219</v>
       </c>
       <c r="C47" t="n">
         <v>58.63854217529297</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>34.56755828857422</v>
+        <v>34.56755065917969</v>
       </c>
       <c r="C48" t="n">
         <v>63.25024032592773</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>33.68580627441406</v>
+        <v>33.68581008911133</v>
       </c>
       <c r="C49" t="n">
         <v>61.08341217041016</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>31.40167236328125</v>
+        <v>31.40167427062988</v>
       </c>
       <c r="C50" t="n">
         <v>56.9415168762207</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>32.11545944213867</v>
+        <v>32.1154670715332</v>
       </c>
       <c r="C51" t="n">
         <v>58.23585891723633</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>33.61465454101562</v>
+        <v>33.61463928222656</v>
       </c>
       <c r="C52" t="n">
         <v>60.28763198852539</v>
@@ -1499,7 +1511,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>32.44923782348633</v>
+        <v>32.44924926757812</v>
       </c>
       <c r="C54" t="n">
         <v>58.19750595092773</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>32.76564025878906</v>
+        <v>32.76564788818359</v>
       </c>
       <c r="C55" t="n">
         <v>58.13039398193359</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>34.65169525146484</v>
+        <v>34.65169906616211</v>
       </c>
       <c r="C56" t="n">
         <v>61.47650909423828</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>34.80302429199219</v>
+        <v>34.80302047729492</v>
       </c>
       <c r="C57" t="n">
         <v>61.74496459960938</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>35.50751113891602</v>
+        <v>35.50751495361328</v>
       </c>
       <c r="C58" t="n">
         <v>62.36816787719727</v>
@@ -1649,7 +1661,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1674,7 +1686,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>34.78095245361328</v>
+        <v>34.78094863891602</v>
       </c>
       <c r="C61" t="n">
         <v>60.44103622436523</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>35.71335983276367</v>
+        <v>35.71337127685547</v>
       </c>
       <c r="C62" t="n">
         <v>62.06135940551758</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>36.35889053344727</v>
+        <v>36.35887908935547</v>
       </c>
       <c r="C63" t="n">
         <v>63.18312454223633</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>36.40048599243164</v>
+        <v>36.4005012512207</v>
       </c>
       <c r="C64" t="n">
         <v>62.57909774780273</v>
@@ -1807,7 +1819,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>38.09029388427734</v>
+        <v>38.09029769897461</v>
       </c>
       <c r="C66" t="n">
         <v>65.48417663574219</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>37.51843643188477</v>
+        <v>37.5184440612793</v>
       </c>
       <c r="C67" t="n">
         <v>63.81591415405273</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>36.84202575683594</v>
+        <v>36.84202194213867</v>
       </c>
       <c r="C68" t="n">
         <v>62.66538619995117</v>
@@ -1923,7 +1935,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>40.4415283203125</v>
+        <v>40.44154357910156</v>
       </c>
       <c r="C70" t="n">
         <v>68.08245086669922</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>39.70115280151367</v>
+        <v>39.70116424560547</v>
       </c>
       <c r="C71" t="n">
         <v>66.83605194091797</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>40.70351409912109</v>
+        <v>40.7035026550293</v>
       </c>
       <c r="C72" t="n">
         <v>68.52349090576172</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>42.31222152709961</v>
+        <v>42.31221389770508</v>
       </c>
       <c r="C73" t="n">
         <v>70.52732849121094</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>41.16180038452148</v>
+        <v>41.16180419921875</v>
       </c>
       <c r="C74" t="n">
         <v>68.60977935791016</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>41.92106246948242</v>
+        <v>41.92107772827148</v>
       </c>
       <c r="C75" t="n">
         <v>69.87535858154297</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>42.9397087097168</v>
+        <v>42.93971252441406</v>
       </c>
       <c r="C76" t="n">
         <v>70.84371948242188</v>
@@ -2155,7 +2167,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>46.11267471313477</v>
+        <v>46.11267852783203</v>
       </c>
       <c r="C78" t="n">
         <v>76.07862091064453</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>49.14011764526367</v>
+        <v>49.1401252746582</v>
       </c>
       <c r="C79" t="n">
         <v>80.31639862060547</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>50.98205947875977</v>
+        <v>50.98208618164062</v>
       </c>
       <c r="C80" t="n">
         <v>83.32694244384766</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>49.04039001464844</v>
+        <v>49.04040145874023</v>
       </c>
       <c r="C81" t="n">
         <v>80.15340423583984</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>50.76788711547852</v>
+        <v>50.76789474487305</v>
       </c>
       <c r="C82" t="n">
         <v>82.2435302734375</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>49.38889694213867</v>
+        <v>49.38890838623047</v>
       </c>
       <c r="C83" t="n">
         <v>80.00959014892578</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>50.73235702514648</v>
+        <v>50.73236465454102</v>
       </c>
       <c r="C84" t="n">
         <v>82.18600463867188</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>50.40357208251953</v>
+        <v>50.4035758972168</v>
       </c>
       <c r="C85" t="n">
         <v>80.94918823242188</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>53.43626403808594</v>
+        <v>53.43625259399414</v>
       </c>
       <c r="C86" t="n">
         <v>85.81974792480469</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>56.28385925292969</v>
+        <v>56.28390502929688</v>
       </c>
       <c r="C87" t="n">
         <v>90.39309692382812</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>58.99114990234375</v>
+        <v>58.99114227294922</v>
       </c>
       <c r="C88" t="n">
         <v>93.94055938720703</v>
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>62.12796020507812</v>
+        <v>62.12795639038086</v>
       </c>
       <c r="C89" t="n">
         <v>98.93576049804688</v>
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>58.29876327514648</v>
+        <v>58.29876708984375</v>
       </c>
       <c r="C90" t="n">
         <v>92.83796691894531</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>58.97496795654297</v>
+        <v>58.97493743896484</v>
       </c>
       <c r="C91" t="n">
         <v>93.13518524169922</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>59.98276519775391</v>
+        <v>59.98277282714844</v>
       </c>
       <c r="C92" t="n">
         <v>94.72675323486328</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>56.75289916992188</v>
+        <v>56.75291061401367</v>
       </c>
       <c r="C93" t="n">
         <v>89.62607574462891</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>57.70672988891602</v>
+        <v>57.70675277709961</v>
       </c>
       <c r="C94" t="n">
         <v>90.3355712890625</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>66.14655303955078</v>
+        <v>66.14656829833984</v>
       </c>
       <c r="C95" t="n">
         <v>103.5474624633789</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>66.85701751708984</v>
+        <v>66.85702514648438</v>
       </c>
       <c r="C96" t="n">
         <v>104.6596374511719</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>64.46881103515625</v>
+        <v>64.46882629394531</v>
       </c>
       <c r="C97" t="n">
         <v>100.1534042358398</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>67.49913024902344</v>
+        <v>67.49908447265625</v>
       </c>
       <c r="C98" t="n">
         <v>104.8609771728516</v>
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>68.10391235351562</v>
+        <v>68.10391998291016</v>
       </c>
       <c r="C99" t="n">
         <v>105.8005752563477</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>68.56172180175781</v>
+        <v>68.56169128417969</v>
       </c>
       <c r="C100" t="n">
         <v>105.7046966552734</v>
@@ -2851,7 +2863,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>69.86763763427734</v>
+        <v>69.86765289306641</v>
       </c>
       <c r="C102" t="n">
         <v>107.7181243896484</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>69.69184875488281</v>
+        <v>69.69183349609375</v>
       </c>
       <c r="C103" t="n">
         <v>106.6347045898438</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>65.08625793457031</v>
+        <v>65.08624267578125</v>
       </c>
       <c r="C104" t="n">
         <v>99.58773040771484</v>
@@ -2967,7 +2979,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>67.93308258056641</v>
+        <v>67.93307495117188</v>
       </c>
       <c r="C106" t="n">
         <v>103.1351852416992</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>72.16429901123047</v>
+        <v>72.16429138183594</v>
       </c>
       <c r="C107" t="n">
         <v>109.558967590332</v>
@@ -3054,7 +3066,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>76.65791320800781</v>
+        <v>76.65793609619141</v>
       </c>
       <c r="C109" t="n">
         <v>115.5400009155273</v>
@@ -3112,7 +3124,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3141,7 +3153,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>71.63655090332031</v>
+        <v>71.63657379150391</v>
       </c>
       <c r="C112" t="n">
         <v>107.1100006103516</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>73.36212921142578</v>
+        <v>73.36209869384766</v>
       </c>
       <c r="C113" t="n">
         <v>109.6900024414062</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>72.80699157714844</v>
+        <v>72.80698394775391</v>
       </c>
       <c r="C114" t="n">
         <v>108.8600006103516</v>
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>71.45435333251953</v>
+        <v>71.45438385009766</v>
       </c>
       <c r="C115" t="n">
         <v>105.9700012207031</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>77.52297973632812</v>
+        <v>77.52294158935547</v>
       </c>
       <c r="C116" t="n">
         <v>114.9700012207031</v>
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>71.83196258544922</v>
+        <v>71.83195495605469</v>
       </c>
       <c r="C117" t="n">
         <v>106.5299987792969</v>
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>74.15170288085938</v>
+        <v>74.15168762207031</v>
       </c>
       <c r="C118" t="n">
         <v>109.0400009155273</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>81.40773010253906</v>
+        <v>81.40776062011719</v>
       </c>
       <c r="C119" t="n">
         <v>119.7099990844727</v>
@@ -3402,7 +3414,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>87.20275115966797</v>
+        <v>87.2027587890625</v>
       </c>
       <c r="C121" t="n">
         <v>127.3000030517578</v>
@@ -3460,7 +3472,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>89.25778961181641</v>
+        <v>89.25782012939453</v>
       </c>
       <c r="C123" t="n">
         <v>130.3000030517578</v>
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>92.79022979736328</v>
+        <v>92.79020690917969</v>
       </c>
       <c r="C124" t="n">
         <v>134.5099945068359</v>
@@ -3547,7 +3559,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>87.63714599609375</v>
+        <v>87.63713073730469</v>
       </c>
       <c r="C126" t="n">
         <v>127.0400009155273</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>95.51393127441406</v>
+        <v>95.51396942138672</v>
       </c>
       <c r="C127" t="n">
         <v>137.4799957275391</v>
@@ -3634,7 +3646,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>88.96942901611328</v>
+        <v>88.96942138671875</v>
       </c>
       <c r="C129" t="n">
         <v>128.0599975585938</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>88.26371765136719</v>
+        <v>88.26373291015625</v>
       </c>
       <c r="C130" t="n">
         <v>126.1399993896484</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>80.055908203125</v>
+        <v>80.05592346191406</v>
       </c>
       <c r="C131" t="n">
         <v>114.4100036621094</v>
@@ -3750,11 +3762,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>80.89558410644531</v>
+        <v>80.89556121826172</v>
       </c>
       <c r="C132" t="n">
         <v>115.6100006103516</v>
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>80.50041961669922</v>
+        <v>80.50042724609375</v>
       </c>
       <c r="C133" t="n">
         <v>114.120002746582</v>
@@ -3808,11 +3820,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>85.44529724121094</v>
+        <v>85.44530487060547</v>
       </c>
       <c r="C134" t="n">
         <v>121.129997253418</v>
@@ -3837,7 +3849,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3866,7 +3878,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>92.19634246826172</v>
+        <v>92.19633483886719</v>
       </c>
       <c r="C137" t="n">
         <v>129.75</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>92.18212890625</v>
+        <v>92.18210601806641</v>
       </c>
       <c r="C138" t="n">
         <v>129.7299957275391</v>
@@ -3953,11 +3965,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>92.42617797851562</v>
+        <v>92.42616271972656</v>
       </c>
       <c r="C139" t="n">
         <v>129.1100006103516</v>
@@ -3982,7 +3994,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -4011,11 +4023,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>88.25979614257812</v>
+        <v>88.25980377197266</v>
       </c>
       <c r="C141" t="n">
         <v>123.2900009155273</v>
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>84.92848205566406</v>
+        <v>84.92849731445312</v>
       </c>
       <c r="C142" t="n">
         <v>117.6800003051758</v>
@@ -4069,7 +4081,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4098,7 +4110,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4127,11 +4139,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>87.77611541748047</v>
+        <v>87.77610015869141</v>
       </c>
       <c r="C145" t="n">
         <v>120.6600036621094</v>
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>85.11357879638672</v>
+        <v>85.11356353759766</v>
       </c>
       <c r="C146" t="n">
         <v>117</v>
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>80.69058990478516</v>
+        <v>80.69058227539062</v>
       </c>
       <c r="C147" t="n">
         <v>110.9199981689453</v>
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>80.83921051025391</v>
+        <v>80.83920288085938</v>
       </c>
       <c r="C148" t="n">
         <v>110.129997253418</v>
@@ -4243,7 +4255,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>74.02736663818359</v>
+        <v>74.02735900878906</v>
       </c>
       <c r="C150" t="n">
         <v>100.8499984741211</v>
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>78.09835815429688</v>
+        <v>78.09835052490234</v>
       </c>
       <c r="C151" t="n">
         <v>105.3399963378906</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>84.41503143310547</v>
+        <v>84.41502380371094</v>
       </c>
       <c r="C152" t="n">
         <v>113.8600006103516</v>
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>85.66056060791016</v>
+        <v>85.66055297851562</v>
       </c>
       <c r="C153" t="n">
         <v>115.5400009155273</v>
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>84.98016357421875</v>
+        <v>84.98018646240234</v>
       </c>
       <c r="C154" t="n">
         <v>113.6399993896484</v>
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>77.99568939208984</v>
+        <v>77.99570465087891</v>
       </c>
       <c r="C155" t="n">
         <v>104.3000030517578</v>
@@ -4446,11 +4458,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>86.27388000488281</v>
+        <v>86.27386474609375</v>
       </c>
       <c r="C156" t="n">
         <v>115.370002746582</v>
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>85.96862030029297</v>
+        <v>85.96858978271484</v>
       </c>
       <c r="C157" t="n">
         <v>113.9400024414062</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>84.03707885742188</v>
+        <v>84.03707122802734</v>
       </c>
       <c r="C158" t="n">
         <v>111.379997253418</v>
@@ -4533,11 +4545,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>88.14915466308594</v>
+        <v>88.14913177490234</v>
       </c>
       <c r="C159" t="n">
         <v>116.8300018310547</v>
@@ -4562,11 +4574,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>94.32005310058594</v>
+        <v>94.320068359375</v>
       </c>
       <c r="C160" t="n">
         <v>123.9000015258789</v>
@@ -4591,11 +4603,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>97.73052215576172</v>
+        <v>97.73050689697266</v>
       </c>
       <c r="C161" t="n">
         <v>128.3800048828125</v>
@@ -4620,7 +4632,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>102.2495803833008</v>
+        <v>102.2495651245117</v>
       </c>
       <c r="C163" t="n">
         <v>133.2799987792969</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>104.0677795410156</v>
+        <v>104.0677871704102</v>
       </c>
       <c r="C164" t="n">
         <v>135.6499938964844</v>
@@ -4707,11 +4719,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>108.2565612792969</v>
+        <v>108.256591796875</v>
       </c>
       <c r="C165" t="n">
         <v>141.1100006103516</v>
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>109.7701187133789</v>
+        <v>109.7701644897461</v>
       </c>
       <c r="C166" t="n">
         <v>142.0500030517578</v>
@@ -4765,11 +4777,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>102.683967590332</v>
+        <v>102.6839599609375</v>
       </c>
       <c r="C167" t="n">
         <v>132.8800048828125</v>
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>105.3576889038086</v>
+        <v>105.3577194213867</v>
       </c>
       <c r="C168" t="n">
         <v>136.3399963378906</v>
@@ -4823,11 +4835,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>107.0950469970703</v>
+        <v>107.0950164794922</v>
       </c>
       <c r="C169" t="n">
         <v>137.5500030517578</v>
@@ -4852,11 +4864,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>111.5252456665039</v>
+        <v>111.5252304077148</v>
       </c>
       <c r="C170" t="n">
         <v>143.2400054931641</v>
@@ -4881,11 +4893,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>102.1432189941406</v>
+        <v>102.1432418823242</v>
       </c>
       <c r="C171" t="n">
         <v>131.1900024414062</v>
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>100.282112121582</v>
+        <v>100.2820892333984</v>
       </c>
       <c r="C172" t="n">
         <v>127.870002746582</v>
@@ -4939,11 +4951,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>108.6029815673828</v>
+        <v>108.6029586791992</v>
       </c>
       <c r="C173" t="n">
         <v>138.4799957275391</v>
@@ -4968,11 +4980,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>110.9243698120117</v>
+        <v>110.9243774414062</v>
       </c>
       <c r="C174" t="n">
         <v>141.4400024414062</v>
@@ -4997,7 +5009,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5026,7 +5038,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5055,11 +5067,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>124.664924621582</v>
+        <v>124.6649398803711</v>
       </c>
       <c r="C177" t="n">
         <v>157.7599945068359</v>
@@ -5084,11 +5096,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>117.4869613647461</v>
+        <v>117.4869384765625</v>
       </c>
       <c r="C178" t="n">
         <v>147.6600036621094</v>
@@ -5113,11 +5125,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>105.4963684082031</v>
+        <v>105.4963836669922</v>
       </c>
       <c r="C179" t="n">
         <v>132.5899963378906</v>
@@ -5142,11 +5154,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>110.8432006835938</v>
+        <v>110.8432235717773</v>
       </c>
       <c r="C180" t="n">
         <v>139.3099975585938</v>
@@ -5171,11 +5183,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>108.114875793457</v>
+        <v>108.1149139404297</v>
       </c>
       <c r="C181" t="n">
         <v>134.8300018310547</v>
@@ -5200,11 +5212,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>105.9258193969727</v>
+        <v>105.9257965087891</v>
       </c>
       <c r="C182" t="n">
         <v>132.1000061035156</v>
@@ -5229,11 +5241,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>102.9027709960938</v>
+        <v>102.9028015136719</v>
       </c>
       <c r="C183" t="n">
         <v>128.3300018310547</v>
@@ -5258,11 +5270,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>112.4811248779297</v>
+        <v>112.4810943603516</v>
       </c>
       <c r="C184" t="n">
         <v>139.0500030517578</v>
@@ -5287,11 +5299,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>107.8459777832031</v>
+        <v>107.8459854125977</v>
       </c>
       <c r="C185" t="n">
         <v>133.3200073242188</v>
@@ -5316,11 +5328,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>105.6699523925781</v>
+        <v>105.6699600219727</v>
       </c>
       <c r="C186" t="n">
         <v>130.6300048828125</v>
@@ -5345,11 +5357,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>109.1699676513672</v>
+        <v>109.1699905395508</v>
       </c>
       <c r="C187" t="n">
         <v>133.7799987792969</v>
@@ -5374,11 +5386,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>110.7531127929688</v>
+        <v>110.7531280517578</v>
       </c>
       <c r="C188" t="n">
         <v>135.7200012207031</v>
@@ -5403,11 +5415,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>112.4586334228516</v>
+        <v>112.4586486816406</v>
       </c>
       <c r="C189" t="n">
         <v>137.8099975585938</v>
@@ -5432,11 +5444,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>108.9543685913086</v>
+        <v>108.9543609619141</v>
       </c>
       <c r="C190" t="n">
         <v>132.4400024414062</v>
@@ -5461,11 +5473,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>106.5275039672852</v>
+        <v>106.5274810791016</v>
       </c>
       <c r="C191" t="n">
         <v>129.4900054931641</v>
@@ -5490,7 +5502,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5519,11 +5531,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>118.563346862793</v>
+        <v>118.5632858276367</v>
       </c>
       <c r="C193" t="n">
         <v>142.9199981689453</v>
@@ -5548,11 +5560,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>114.1914138793945</v>
+        <v>114.1914215087891</v>
       </c>
       <c r="C194" t="n">
         <v>137.6499938964844</v>
@@ -5577,11 +5589,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>107.9695816040039</v>
+        <v>107.9696044921875</v>
       </c>
       <c r="C195" t="n">
         <v>130.1499938964844</v>
@@ -5606,11 +5618,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>103.0920181274414</v>
+        <v>103.0920104980469</v>
       </c>
       <c r="C196" t="n">
         <v>123.1600036621094</v>
@@ -5635,11 +5647,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>116.2087020874023</v>
+        <v>116.2087173461914</v>
       </c>
       <c r="C197" t="n">
         <v>138.8300018310547</v>
@@ -5664,11 +5676,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>111.3453903198242</v>
+        <v>111.3454055786133</v>
       </c>
       <c r="C198" t="n">
         <v>133.0200042724609</v>
@@ -5693,11 +5705,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>114.1405029296875</v>
+        <v>114.1404876708984</v>
       </c>
       <c r="C199" t="n">
         <v>135.1499938964844</v>
@@ -5722,7 +5734,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5751,11 +5763,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>107.6966247558594</v>
+        <v>107.6966323852539</v>
       </c>
       <c r="C201" t="n">
         <v>127.5199966430664</v>
@@ -5780,11 +5792,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>95.91838836669922</v>
+        <v>95.91838073730469</v>
       </c>
       <c r="C202" t="n">
         <v>112.5400009155273</v>
@@ -5809,7 +5821,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5838,11 +5850,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>115.5981292724609</v>
+        <v>115.5981216430664</v>
       </c>
       <c r="C204" t="n">
         <v>135.6300048828125</v>
@@ -5867,11 +5879,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>116.6905975341797</v>
+        <v>116.6905822753906</v>
       </c>
       <c r="C205" t="n">
         <v>135.75</v>
@@ -5896,11 +5908,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>111.7564849853516</v>
+        <v>111.756477355957</v>
       </c>
       <c r="C206" t="n">
         <v>130.0099945068359</v>
@@ -5925,11 +5937,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>107.4928817749023</v>
+        <v>107.4929046630859</v>
       </c>
       <c r="C207" t="n">
         <v>125.0500030517578</v>
@@ -5954,11 +5966,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>116.4856948852539</v>
+        <v>116.485710144043</v>
       </c>
       <c r="C208" t="n">
         <v>134.2200012207031</v>
@@ -5983,11 +5995,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>125.7458877563477</v>
+        <v>125.7458724975586</v>
       </c>
       <c r="C209" t="n">
         <v>144.8899993896484</v>
@@ -6012,11 +6024,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>116.5377578735352</v>
+        <v>116.5377655029297</v>
       </c>
       <c r="C210" t="n">
         <v>134.2799987792969</v>
@@ -6041,11 +6053,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>120.8748550415039</v>
+        <v>120.8748321533203</v>
       </c>
       <c r="C211" t="n">
         <v>138.0599975585938</v>
@@ -6070,11 +6082,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>113.0301513671875</v>
+        <v>113.0301666259766</v>
       </c>
       <c r="C212" t="n">
         <v>129.1000061035156</v>
@@ -6099,11 +6111,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>112.7937622070312</v>
+        <v>112.7937469482422</v>
       </c>
       <c r="C213" t="n">
         <v>128.8300018310547</v>
@@ -6128,11 +6140,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>106.8026428222656</v>
+        <v>106.8026351928711</v>
       </c>
       <c r="C214" t="n">
         <v>120.8499984741211</v>
@@ -6157,11 +6169,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>105.7332763671875</v>
+        <v>105.733283996582</v>
       </c>
       <c r="C215" t="n">
         <v>119.6399993896484</v>
@@ -6186,11 +6198,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>109.3478622436523</v>
+        <v>109.3478698730469</v>
       </c>
       <c r="C216" t="n">
         <v>123.7300033569336</v>
@@ -6215,7 +6227,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6244,11 +6256,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>107.9489440917969</v>
+        <v>107.9489517211914</v>
       </c>
       <c r="C218" t="n">
         <v>120.9700012207031</v>
@@ -6273,11 +6285,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>108.1274108886719</v>
+        <v>108.1274185180664</v>
       </c>
       <c r="C219" t="n">
         <v>121.1699981689453</v>
@@ -6302,7 +6314,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6331,11 +6343,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>123.036750793457</v>
+        <v>123.0367584228516</v>
       </c>
       <c r="C221" t="n">
         <v>136.5299987792969</v>
@@ -6360,11 +6372,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>120.1259689331055</v>
+        <v>120.1259536743164</v>
       </c>
       <c r="C222" t="n">
         <v>133.3000030517578</v>
@@ -6389,11 +6401,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>125.6607360839844</v>
+        <v>125.6607208251953</v>
       </c>
       <c r="C223" t="n">
         <v>138.1999969482422</v>
@@ -6418,7 +6430,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6447,11 +6459,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>131.5345916748047</v>
+        <v>131.5346069335938</v>
       </c>
       <c r="C225" t="n">
         <v>144.6600036621094</v>
@@ -6476,11 +6488,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>130.4454650878906</v>
+        <v>130.4454956054688</v>
       </c>
       <c r="C226" t="n">
         <v>142.2799987792969</v>
@@ -6505,11 +6517,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>123.0191879272461</v>
+        <v>123.0192108154297</v>
       </c>
       <c r="C227" t="n">
         <v>134.1799926757812</v>
@@ -6534,11 +6546,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>127.7591781616211</v>
+        <v>127.7591934204102</v>
       </c>
       <c r="C228" t="n">
         <v>139.3500061035156</v>
@@ -6563,11 +6575,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>121.2108001708984</v>
+        <v>121.2107925415039</v>
       </c>
       <c r="C229" t="n">
         <v>131.0399932861328</v>
@@ -6592,7 +6604,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6621,7 +6633,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6650,7 +6662,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6679,11 +6691,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>122.9834060668945</v>
+        <v>122.9834136962891</v>
       </c>
       <c r="C233" t="n">
         <v>131.7799987792969</v>
@@ -6708,7 +6720,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6737,7 +6749,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6766,7 +6778,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6795,7 +6807,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6824,7 +6836,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6853,7 +6865,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6882,7 +6894,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6911,7 +6923,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6940,7 +6952,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6969,7 +6981,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6998,7 +7010,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7027,7 +7039,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7056,7 +7068,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7085,7 +7097,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7114,7 +7126,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7143,7 +7155,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7172,32 +7184,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>97.69999694824219</v>
+        <v>97.22000122070312</v>
       </c>
       <c r="C250" t="n">
-        <v>97.69999694824219</v>
+        <v>97.22000122070312</v>
       </c>
       <c r="D250" t="n">
-        <v>80810700</v>
+        <v>84463300</v>
       </c>
       <c r="E250" t="n">
         <v>5.88</v>
       </c>
       <c r="F250" t="n">
-        <v>16.61564573949697</v>
+        <v>16.53401381304475</v>
       </c>
       <c r="G250" t="n">
         <v>332579038</v>
       </c>
       <c r="H250" t="n">
-        <v>32492970997.64932</v>
+        <v>32333334480.34027</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2429819404312547</v>
+        <v>0.2539645929218185</v>
       </c>
     </row>
   </sheetData>
@@ -7229,75 +7241,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7333,13 +7345,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7375,13 +7387,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7417,13 +7429,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7450,7 +7462,7 @@
       <c r="I5" t="n">
         <v>4.332677783881691</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K5" t="n">
@@ -7463,13 +7475,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7496,7 +7508,7 @@
       <c r="I6" t="n">
         <v>4.275151417630492</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K6" t="n">
@@ -7509,13 +7521,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7542,7 +7554,7 @@
       <c r="I7" t="n">
         <v>4.494983283764443</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K7" t="n">
@@ -7555,13 +7567,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7588,7 +7600,7 @@
       <c r="I8" t="n">
         <v>4.245702363342583</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K8" t="n">
@@ -7601,13 +7613,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7634,7 +7646,7 @@
       <c r="I9" t="n">
         <v>4.274465546468182</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K9" t="n">
@@ -7647,13 +7659,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7680,7 +7692,7 @@
       <c r="I10" t="n">
         <v>4.216939180216984</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="K10" t="n">
@@ -7693,13 +7705,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7726,7 +7738,7 @@
       <c r="I11" t="n">
         <v>4.055608820709492</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K11" t="n">
@@ -7739,13 +7751,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7772,7 +7784,7 @@
       <c r="I12" t="n">
         <v>4.007670182166827</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K12" t="n">
@@ -7785,13 +7797,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7818,7 +7830,7 @@
       <c r="I13" t="n">
         <v>3.825503355704698</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K13" t="n">
@@ -7831,13 +7843,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7864,7 +7876,7 @@
       <c r="I14" t="n">
         <v>4.132310642377757</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="K14" t="n">
@@ -7877,13 +7889,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7910,7 +7922,7 @@
       <c r="I15" t="n">
         <v>4.352828379674017</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="K15" t="n">
@@ -7923,13 +7935,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41218</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7956,7 +7968,7 @@
       <c r="I16" t="n">
         <v>4.554170661553212</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41218</v>
       </c>
       <c r="K16" t="n">
@@ -7969,13 +7981,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8002,7 +8014,7 @@
       <c r="I17" t="n">
         <v>4.23777564717162</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K17" t="n">
@@ -8015,13 +8027,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8048,7 +8060,7 @@
       <c r="I18" t="n">
         <v>4.410354745925217</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K18" t="n">
@@ -8061,13 +8073,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8094,7 +8106,7 @@
       <c r="I19" t="n">
         <v>4.506232023010547</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="K19" t="n">
@@ -8107,13 +8119,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8140,7 +8152,7 @@
       <c r="I20" t="n">
         <v>4.621284755512944</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="K20" t="n">
@@ -8153,13 +8165,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8186,7 +8198,7 @@
       <c r="I21" t="n">
         <v>5.302013422818793</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="K21" t="n">
@@ -8199,13 +8211,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41750</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8232,7 +8244,7 @@
       <c r="I22" t="n">
         <v>5.349952061361458</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41750</v>
       </c>
       <c r="K22" t="n">
@@ -8245,13 +8257,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41842</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8278,7 +8290,7 @@
       <c r="I23" t="n">
         <v>5.340364333652925</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41842</v>
       </c>
       <c r="K23" t="n">
@@ -8291,13 +8303,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41933</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8324,7 +8336,7 @@
       <c r="I24" t="n">
         <v>5.41706615532119</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41933</v>
       </c>
       <c r="K24" t="n">
@@ -8337,13 +8349,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42053</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8370,7 +8382,7 @@
       <c r="I25" t="n">
         <v>4.04</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42053</v>
       </c>
       <c r="K25" t="n">
@@ -8383,13 +8395,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42115</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8416,7 +8428,7 @@
       <c r="I26" t="n">
         <v>3.958130393096836</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42115</v>
       </c>
       <c r="K26" t="n">
@@ -8429,13 +8441,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8462,7 +8474,7 @@
       <c r="I27" t="n">
         <v>1.83378715244487</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="K27" t="n">
@@ -8475,13 +8487,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8508,7 +8520,7 @@
       <c r="I28" t="n">
         <v>1.805627996164909</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="K28" t="n">
@@ -8521,13 +8533,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8554,7 +8566,7 @@
       <c r="I29" t="n">
         <v>2.77</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="K29" t="n">
@@ -8567,13 +8579,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8600,7 +8612,7 @@
       <c r="I30" t="n">
         <v>3</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="K30" t="n">
@@ -8613,13 +8625,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42576</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8646,7 +8658,7 @@
       <c r="I31" t="n">
         <v>5.390000000000001</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42576</v>
       </c>
       <c r="K31" t="n">
@@ -8659,13 +8671,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42667</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8692,7 +8704,7 @@
       <c r="I32" t="n">
         <v>5.5</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42667</v>
       </c>
       <c r="K32" t="n">
@@ -8705,13 +8717,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42774</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8738,7 +8750,7 @@
       <c r="I33" t="n">
         <v>5.99</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42774</v>
       </c>
       <c r="K33" t="n">
@@ -8751,13 +8763,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8784,7 +8796,7 @@
       <c r="I34" t="n">
         <v>6.06</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="K34" t="n">
@@ -8797,13 +8809,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8830,7 +8842,7 @@
       <c r="I35" t="n">
         <v>5.99</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="K35" t="n">
@@ -8843,13 +8855,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43031</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8876,7 +8888,7 @@
       <c r="I36" t="n">
         <v>6.07</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43031</v>
       </c>
       <c r="K36" t="n">
@@ -8889,13 +8901,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8922,7 +8934,7 @@
       <c r="I37" t="n">
         <v>6.4</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="K37" t="n">
@@ -8935,13 +8947,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43213</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8968,7 +8980,7 @@
       <c r="I38" t="n">
         <v>5.09</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43213</v>
       </c>
       <c r="K38" t="n">
@@ -8981,13 +8993,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43305</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9014,7 +9026,7 @@
       <c r="I39" t="n">
         <v>4.9</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43305</v>
       </c>
       <c r="K39" t="n">
@@ -9027,13 +9039,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43395</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9060,7 +9072,7 @@
       <c r="I40" t="n">
         <v>4.59</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43395</v>
       </c>
       <c r="K40" t="n">
@@ -9073,13 +9085,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9106,7 +9118,7 @@
       <c r="I41" t="n">
         <v>4.03</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="K41" t="n">
@@ -9119,13 +9131,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43577</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9152,7 +9164,7 @@
       <c r="I42" t="n">
         <v>5.08</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43577</v>
       </c>
       <c r="K42" t="n">
@@ -9165,13 +9177,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43669</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9198,7 +9210,7 @@
       <c r="I43" t="n">
         <v>5.18</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43669</v>
       </c>
       <c r="K43" t="n">
@@ -9211,13 +9223,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43760</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9244,7 +9256,7 @@
       <c r="I44" t="n">
         <v>5.83</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43760</v>
       </c>
       <c r="K44" t="n">
@@ -9257,13 +9269,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9290,7 +9302,7 @@
       <c r="I45" t="n">
         <v>6.24</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="K45" t="n">
@@ -9303,13 +9315,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43943</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9336,7 +9348,7 @@
       <c r="I46" t="n">
         <v>6.85</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43943</v>
       </c>
       <c r="K46" t="n">
@@ -9349,13 +9361,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9382,7 +9394,7 @@
       <c r="I47" t="n">
         <v>7.44</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="K47" t="n">
@@ -9395,13 +9407,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9428,7 +9440,7 @@
       <c r="I48" t="n">
         <v>6.88</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="K48" t="n">
@@ -9441,13 +9453,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9474,7 +9486,7 @@
       <c r="I49" t="n">
         <v>6.87</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="K49" t="n">
@@ -9487,13 +9499,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9520,7 +9532,7 @@
       <c r="I50" t="n">
         <v>6.67</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="K50" t="n">
@@ -9533,13 +9545,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9566,7 +9578,7 @@
       <c r="I51" t="n">
         <v>5.869999999999999</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="K51" t="n">
@@ -9579,13 +9591,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44494</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9612,7 +9624,7 @@
       <c r="I52" t="n">
         <v>5.88</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44494</v>
       </c>
       <c r="K52" t="n">
@@ -9625,13 +9637,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44602</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9658,7 +9670,7 @@
       <c r="I53" t="n">
         <v>5.35</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44602</v>
       </c>
       <c r="K53" t="n">
@@ -9671,13 +9683,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9704,7 +9716,7 @@
       <c r="I54" t="n">
         <v>5.18</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="K54" t="n">
@@ -9717,13 +9729,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44768</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9750,7 +9762,7 @@
       <c r="I55" t="n">
         <v>5.279999999999999</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44768</v>
       </c>
       <c r="K55" t="n">
@@ -9763,13 +9775,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9796,7 +9808,7 @@
       <c r="I56" t="n">
         <v>5.27</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="K56" t="n">
@@ -9809,13 +9821,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44966</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9842,7 +9854,7 @@
       <c r="I57" t="n">
         <v>5.720000000000001</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44966</v>
       </c>
       <c r="K57" t="n">
@@ -9855,13 +9867,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9888,7 +9900,7 @@
       <c r="I58" t="n">
         <v>5.84</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="K58" t="n">
@@ -9901,13 +9913,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9934,7 +9946,7 @@
       <c r="I59" t="n">
         <v>4.850000000000001</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="K59" t="n">
@@ -9947,13 +9959,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9980,7 +9992,7 @@
       <c r="I60" t="n">
         <v>5.2</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="K60" t="n">
@@ -9993,13 +10005,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10026,7 +10038,7 @@
       <c r="I61" t="n">
         <v>5.21</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="K61" t="n">
@@ -10039,13 +10051,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10072,7 +10084,7 @@
       <c r="I62" t="n">
         <v>5.449999999999999</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="K62" t="n">
@@ -10085,13 +10097,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10118,7 +10130,7 @@
       <c r="I63" t="n">
         <v>6.76</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="K63" t="n">
@@ -10131,13 +10143,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10164,7 +10176,7 @@
       <c r="I64" t="n">
         <v>7.72</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="K64" t="n">
@@ -10177,13 +10189,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10210,7 +10222,7 @@
       <c r="I65" t="n">
         <v>7.55</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="K65" t="n">
@@ -10223,13 +10235,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10256,7 +10268,7 @@
       <c r="I66" t="n">
         <v>7.340000000000001</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="K66" t="n">
@@ -10269,13 +10281,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10302,7 +10314,7 @@
       <c r="I67" t="n">
         <v>7.26</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K67" t="n">
@@ -10315,13 +10327,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10348,7 +10360,7 @@
       <c r="I68" t="n">
         <v>5.91</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="K68" t="n">
@@ -10361,13 +10373,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10394,7 +10406,7 @@
       <c r="I69" t="n">
         <v>6.07</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="K69" t="n">
@@ -10407,13 +10419,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10440,7 +10452,7 @@
       <c r="I70" t="n">
         <v>6.37</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="K70" t="n">
@@ -10453,13 +10465,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10486,7 +10498,7 @@
       <c r="I71" t="n">
         <v>5.88</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="K71" t="n">
@@ -10523,52 +10535,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="C2" t="n">
@@ -10597,10 +10609,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40116</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10629,10 +10641,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40221</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40233</v>
       </c>
       <c r="C4" t="n">
@@ -10661,10 +10673,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10693,10 +10705,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="C6" t="n">
@@ -10725,10 +10737,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="C7" t="n">
@@ -10757,10 +10769,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40585</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="C8" t="n">
@@ -10789,10 +10801,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="C9" t="n">
@@ -10821,10 +10833,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C10" t="n">
@@ -10853,10 +10865,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C11" t="n">
@@ -10885,10 +10897,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40961</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="C12" t="n">
@@ -10917,10 +10929,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41026</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="C13" t="n">
@@ -10949,10 +10961,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41117</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="C14" t="n">
@@ -10981,10 +10993,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41211</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41218</v>
       </c>
       <c r="C15" t="n">
@@ -11013,10 +11025,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41320</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C16" t="n">
@@ -11045,10 +11057,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41389</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C17" t="n">
@@ -11077,10 +11089,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41481</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="C18" t="n">
@@ -11109,10 +11121,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41572</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C19" t="n">
@@ -11141,10 +11153,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41677</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="C20" t="n">
@@ -11173,10 +11185,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41743</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41750</v>
       </c>
       <c r="C21" t="n">
@@ -11205,10 +11217,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41835</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41842</v>
       </c>
       <c r="C22" t="n">
@@ -11237,10 +11249,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41926</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41933</v>
       </c>
       <c r="C23" t="n">
@@ -11269,10 +11281,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42046</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42053</v>
       </c>
       <c r="C24" t="n">
@@ -11301,10 +11313,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42108</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42115</v>
       </c>
       <c r="C25" t="n">
@@ -11333,10 +11345,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42201</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="C26" t="n">
@@ -11365,10 +11377,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42291</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="C27" t="n">
@@ -11397,10 +11409,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42404</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="C28" t="n">
@@ -11429,10 +11441,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42475</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="C29" t="n">
@@ -11461,10 +11473,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42569</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42576</v>
       </c>
       <c r="C30" t="n">
@@ -11493,10 +11505,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42660</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42667</v>
       </c>
       <c r="C31" t="n">
@@ -11525,10 +11537,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42767</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42774</v>
       </c>
       <c r="C32" t="n">
@@ -11557,10 +11569,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42842</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="C33" t="n">
@@ -11589,10 +11601,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42934</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="C34" t="n">
@@ -11621,10 +11633,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43024</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43031</v>
       </c>
       <c r="C35" t="n">
@@ -11653,10 +11665,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43132</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="C36" t="n">
@@ -11685,10 +11697,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43206</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43213</v>
       </c>
       <c r="C37" t="n">
@@ -11717,10 +11729,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43298</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43305</v>
       </c>
       <c r="C38" t="n">
@@ -11749,10 +11761,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43388</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43395</v>
       </c>
       <c r="C39" t="n">
@@ -11781,10 +11793,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="C40" t="n">
@@ -11813,10 +11825,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43570</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43577</v>
       </c>
       <c r="C41" t="n">
@@ -11845,10 +11857,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43662</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43669</v>
       </c>
       <c r="C42" t="n">
@@ -11877,10 +11889,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43753</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43760</v>
       </c>
       <c r="C43" t="n">
@@ -11909,10 +11921,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="C44" t="n">
@@ -11941,10 +11953,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43936</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43943</v>
       </c>
       <c r="C45" t="n">
@@ -11973,10 +11985,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44028</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="C46" t="n">
@@ -12005,10 +12017,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44119</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="C47" t="n">
@@ -12037,10 +12049,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="C48" t="n">
@@ -12069,10 +12081,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44302</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="C49" t="n">
@@ -12101,10 +12113,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44393</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="C50" t="n">
@@ -12133,10 +12145,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44487</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44494</v>
       </c>
       <c r="C51" t="n">
@@ -12165,10 +12177,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44602</v>
       </c>
       <c r="C52" t="n">
@@ -12197,10 +12209,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44666</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="C53" t="n">
@@ -12229,10 +12241,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44761</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44768</v>
       </c>
       <c r="C54" t="n">
@@ -12261,10 +12273,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44852</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="C55" t="n">
@@ -12293,10 +12305,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44966</v>
       </c>
       <c r="C56" t="n">
@@ -12325,10 +12337,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45034</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="C57" t="n">
@@ -12357,10 +12369,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45125</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="C58" t="n">
@@ -12389,10 +12401,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45216</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="C59" t="n">
@@ -12421,10 +12433,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="C60" t="n">
@@ -12453,10 +12465,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45398</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="C61" t="n">
@@ -12485,10 +12497,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45489</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="C62" t="n">
@@ -12517,10 +12529,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45580</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="C63" t="n">
@@ -12549,10 +12561,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="C64" t="n">
@@ -12581,10 +12593,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45762</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="C65" t="n">
@@ -12613,10 +12625,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45863</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C66" t="n">
@@ -12645,10 +12657,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45953</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C67" t="n">
@@ -12677,10 +12689,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="C68" t="n">
@@ -12709,10 +12721,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="C69" t="n">
@@ -12741,10 +12753,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46231</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C70" t="n">
@@ -12791,12 +12803,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -12867,7 +12879,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">

--- a/salidas/empresas/KMB.xlsx
+++ b/salidas/empresas/KMB.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>26.16888618469238</v>
+        <v>26.16888427734375</v>
       </c>
       <c r="C2" t="n">
         <v>54.76510238647461</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>27.11264801025391</v>
+        <v>27.11265182495117</v>
       </c>
       <c r="C3" t="n">
         <v>56.74017333984375</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>26.70279884338379</v>
+        <v>26.70278549194336</v>
       </c>
       <c r="C4" t="n">
         <v>55.41706466674805</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>27.0400333404541</v>
+        <v>27.0400505065918</v>
       </c>
       <c r="C5" t="n">
         <v>56.11697006225586</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>28.0286865234375</v>
+        <v>28.02869033813477</v>
       </c>
       <c r="C6" t="n">
         <v>58.16874313354492</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>28.73846244812012</v>
+        <v>28.73846054077148</v>
       </c>
       <c r="C7" t="n">
         <v>59.15628051757812</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>28.43570899963379</v>
+        <v>28.43569946289062</v>
       </c>
       <c r="C8" t="n">
         <v>58.53307723999023</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>30.67729949951172</v>
+        <v>30.67731285095215</v>
       </c>
       <c r="C10" t="n">
         <v>62.66538619995117</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>31.22177696228027</v>
+        <v>31.22176933288574</v>
       </c>
       <c r="C11" t="n">
         <v>63.77756500244141</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>31.19830131530762</v>
+        <v>31.19829559326172</v>
       </c>
       <c r="C12" t="n">
         <v>63.7296257019043</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>32.12498474121094</v>
+        <v>32.12497711181641</v>
       </c>
       <c r="C13" t="n">
         <v>65.14861297607422</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>32.81050109863281</v>
+        <v>32.81050872802734</v>
       </c>
       <c r="C14" t="n">
         <v>66.53883361816406</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>32.14861679077148</v>
+        <v>32.14862060546875</v>
       </c>
       <c r="C15" t="n">
         <v>65.19654846191406</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>32.63455581665039</v>
+        <v>32.63456726074219</v>
       </c>
       <c r="C16" t="n">
         <v>65.66634368896484</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>33.91154479980469</v>
+        <v>33.91153717041016</v>
       </c>
       <c r="C17" t="n">
         <v>68.23585510253906</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>33.81149291992188</v>
+        <v>33.81148910522461</v>
       </c>
       <c r="C18" t="n">
         <v>68.03451538085938</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>32.291015625</v>
+        <v>32.29100799560547</v>
       </c>
       <c r="C20" t="n">
         <v>64.49664306640625</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>32.97265243530273</v>
+        <v>32.97263717651367</v>
       </c>
       <c r="C21" t="n">
         <v>65.85810089111328</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>33.98675537109375</v>
+        <v>33.98677825927734</v>
       </c>
       <c r="C22" t="n">
         <v>67.36337280273438</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>34.29150772094727</v>
+        <v>34.2915153503418</v>
       </c>
       <c r="C23" t="n">
         <v>67.96739959716797</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>33.76910400390625</v>
+        <v>33.76908493041992</v>
       </c>
       <c r="C24" t="n">
         <v>66.93193054199219</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>33.80347442626953</v>
+        <v>33.80345916748047</v>
       </c>
       <c r="C25" t="n">
         <v>66.48130035400391</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>31.99483489990234</v>
+        <v>31.99484062194824</v>
       </c>
       <c r="C26" t="n">
         <v>62.92425537109375</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>31.77546501159668</v>
+        <v>31.77546310424805</v>
       </c>
       <c r="C27" t="n">
         <v>62.4928092956543</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>31.75168800354004</v>
+        <v>31.75170135498047</v>
       </c>
       <c r="C28" t="n">
         <v>61.8887825012207</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>31.38276290893555</v>
+        <v>31.38277435302734</v>
       </c>
       <c r="C30" t="n">
         <v>61.16970443725586</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>29.67824363708496</v>
+        <v>29.67826080322266</v>
       </c>
       <c r="C31" t="n">
         <v>57.31543731689453</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>28.71015739440918</v>
+        <v>28.71014595031738</v>
       </c>
       <c r="C32" t="n">
         <v>55.44582748413086</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>30.62151718139648</v>
+        <v>30.62152671813965</v>
       </c>
       <c r="C33" t="n">
         <v>59.13710403442383</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>32.49001693725586</v>
+        <v>32.49001312255859</v>
       </c>
       <c r="C34" t="n">
         <v>62.16682434082031</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>28.95740127563477</v>
+        <v>28.9573974609375</v>
       </c>
       <c r="C36" t="n">
         <v>55.40747833251953</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>26.69798469543457</v>
+        <v>26.69799423217773</v>
       </c>
       <c r="C37" t="n">
         <v>50.56567764282227</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>23.84798049926758</v>
+        <v>23.84798240661621</v>
       </c>
       <c r="C39" t="n">
         <v>45.16778564453125</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>26.61410331726074</v>
+        <v>26.61408805847168</v>
       </c>
       <c r="C42" t="n">
         <v>49.75071716308594</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>27.19382858276367</v>
+        <v>27.1938304901123</v>
       </c>
       <c r="C43" t="n">
         <v>50.26845550537109</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>30.31621551513672</v>
+        <v>30.31621170043945</v>
       </c>
       <c r="C44" t="n">
         <v>56.04026794433594</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>31.35874366760254</v>
+        <v>31.35873794555664</v>
       </c>
       <c r="C45" t="n">
         <v>57.96740341186523</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>30.90486335754395</v>
+        <v>30.90487480163574</v>
       </c>
       <c r="C46" t="n">
         <v>56.54841613769531</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>32.04716491699219</v>
+        <v>32.04715728759766</v>
       </c>
       <c r="C47" t="n">
         <v>58.63854217529297</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>34.56755065917969</v>
+        <v>34.56755447387695</v>
       </c>
       <c r="C48" t="n">
         <v>63.25024032592773</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>33.68581008911133</v>
+        <v>33.68580627441406</v>
       </c>
       <c r="C49" t="n">
         <v>61.08341217041016</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>31.40167427062988</v>
+        <v>31.40166854858398</v>
       </c>
       <c r="C50" t="n">
         <v>56.9415168762207</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>32.1154670715332</v>
+        <v>32.11546325683594</v>
       </c>
       <c r="C51" t="n">
         <v>58.23585891723633</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>32.74861526489258</v>
+        <v>32.74861145019531</v>
       </c>
       <c r="C53" t="n">
         <v>58.73442077636719</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>32.44924926757812</v>
+        <v>32.44923782348633</v>
       </c>
       <c r="C54" t="n">
         <v>58.19750595092773</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>32.76564788818359</v>
+        <v>32.76564025878906</v>
       </c>
       <c r="C55" t="n">
         <v>58.13039398193359</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>34.65169906616211</v>
+        <v>34.65171813964844</v>
       </c>
       <c r="C56" t="n">
         <v>61.47650909423828</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>34.80302047729492</v>
+        <v>34.80302810668945</v>
       </c>
       <c r="C57" t="n">
         <v>61.74496459960938</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>35.50751495361328</v>
+        <v>35.50749206542969</v>
       </c>
       <c r="C58" t="n">
         <v>62.36816787719727</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>33.78261947631836</v>
+        <v>33.78261566162109</v>
       </c>
       <c r="C60" t="n">
         <v>59.33844757080078</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>34.78094863891602</v>
+        <v>34.78096008300781</v>
       </c>
       <c r="C61" t="n">
         <v>60.44103622436523</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>36.35887908935547</v>
+        <v>36.3588981628418</v>
       </c>
       <c r="C63" t="n">
         <v>63.18312454223633</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>36.4005012512207</v>
+        <v>36.40048599243164</v>
       </c>
       <c r="C64" t="n">
         <v>62.57909774780273</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>36.84106826782227</v>
+        <v>36.841064453125</v>
       </c>
       <c r="C65" t="n">
         <v>63.33652877807617</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>38.09029769897461</v>
+        <v>38.09029006958008</v>
       </c>
       <c r="C66" t="n">
         <v>65.48417663574219</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>37.5184440612793</v>
+        <v>37.51843643188477</v>
       </c>
       <c r="C67" t="n">
         <v>63.81591415405273</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>36.84202194213867</v>
+        <v>36.84203338623047</v>
       </c>
       <c r="C68" t="n">
         <v>62.66538619995117</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>40.44154357910156</v>
+        <v>40.4415397644043</v>
       </c>
       <c r="C70" t="n">
         <v>68.08245086669922</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>39.70116424560547</v>
+        <v>39.701171875</v>
       </c>
       <c r="C71" t="n">
         <v>66.83605194091797</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>40.7035026550293</v>
+        <v>40.70352172851562</v>
       </c>
       <c r="C72" t="n">
         <v>68.52349090576172</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>42.31221389770508</v>
+        <v>42.31220626831055</v>
       </c>
       <c r="C73" t="n">
         <v>70.52732849121094</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>41.16180419921875</v>
+        <v>41.16179275512695</v>
       </c>
       <c r="C74" t="n">
         <v>68.60977935791016</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>41.92107772827148</v>
+        <v>41.92105865478516</v>
       </c>
       <c r="C75" t="n">
         <v>69.87535858154297</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>45.60128784179688</v>
+        <v>45.60128402709961</v>
       </c>
       <c r="C77" t="n">
         <v>75.23490142822266</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>46.11267852783203</v>
+        <v>46.1126594543457</v>
       </c>
       <c r="C78" t="n">
         <v>76.07862091064453</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>49.1401252746582</v>
+        <v>49.14011001586914</v>
       </c>
       <c r="C79" t="n">
         <v>80.31639862060547</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>50.98208618164062</v>
+        <v>50.9820556640625</v>
       </c>
       <c r="C80" t="n">
         <v>83.32694244384766</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>49.04040145874023</v>
+        <v>49.0403938293457</v>
       </c>
       <c r="C81" t="n">
         <v>80.15340423583984</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>50.76789474487305</v>
+        <v>50.76789093017578</v>
       </c>
       <c r="C82" t="n">
         <v>82.2435302734375</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>49.38890838623047</v>
+        <v>49.38888549804688</v>
       </c>
       <c r="C83" t="n">
         <v>80.00959014892578</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>50.73236465454102</v>
+        <v>50.73237609863281</v>
       </c>
       <c r="C84" t="n">
         <v>82.18600463867188</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>50.4035758972168</v>
+        <v>50.40358352661133</v>
       </c>
       <c r="C85" t="n">
         <v>80.94918823242188</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>53.43625259399414</v>
+        <v>53.43624114990234</v>
       </c>
       <c r="C86" t="n">
         <v>85.81974792480469</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>56.28390502929688</v>
+        <v>56.28389358520508</v>
       </c>
       <c r="C87" t="n">
         <v>90.39309692382812</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>58.99114227294922</v>
+        <v>58.99116516113281</v>
       </c>
       <c r="C88" t="n">
         <v>93.94055938720703</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>62.12795639038086</v>
+        <v>62.12796401977539</v>
       </c>
       <c r="C89" t="n">
         <v>98.93576049804688</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>58.29876708984375</v>
+        <v>58.29877090454102</v>
       </c>
       <c r="C90" t="n">
         <v>92.83796691894531</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>58.97493743896484</v>
+        <v>58.9749641418457</v>
       </c>
       <c r="C91" t="n">
         <v>93.13518524169922</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>59.98277282714844</v>
+        <v>59.98276519775391</v>
       </c>
       <c r="C92" t="n">
         <v>94.72675323486328</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>66.14656829833984</v>
+        <v>66.14655303955078</v>
       </c>
       <c r="C95" t="n">
         <v>103.5474624633789</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>66.85702514648438</v>
+        <v>66.85700225830078</v>
       </c>
       <c r="C96" t="n">
         <v>104.6596374511719</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>64.46882629394531</v>
+        <v>64.46885681152344</v>
       </c>
       <c r="C97" t="n">
         <v>100.1534042358398</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>67.49908447265625</v>
+        <v>67.49910736083984</v>
       </c>
       <c r="C98" t="n">
         <v>104.8609771728516</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>68.56169128417969</v>
+        <v>68.56169891357422</v>
       </c>
       <c r="C100" t="n">
         <v>105.7046966552734</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>69.80545806884766</v>
+        <v>69.80545043945312</v>
       </c>
       <c r="C101" t="n">
         <v>107.6222457885742</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>69.86765289306641</v>
+        <v>69.86763000488281</v>
       </c>
       <c r="C102" t="n">
         <v>107.7181243896484</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>69.69183349609375</v>
+        <v>69.69185638427734</v>
       </c>
       <c r="C103" t="n">
         <v>106.6347045898438</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>65.08624267578125</v>
+        <v>65.08623504638672</v>
       </c>
       <c r="C104" t="n">
         <v>99.58773040771484</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>67.67416381835938</v>
+        <v>67.67413330078125</v>
       </c>
       <c r="C105" t="n">
         <v>103.5474624633789</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>67.93307495117188</v>
+        <v>67.93305969238281</v>
       </c>
       <c r="C106" t="n">
         <v>103.1351852416992</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>76.79549407958984</v>
+        <v>76.79547882080078</v>
       </c>
       <c r="C108" t="n">
         <v>116.5899963378906</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>76.65793609619141</v>
+        <v>76.65795135498047</v>
       </c>
       <c r="C109" t="n">
         <v>115.5400009155273</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>72.75669097900391</v>
+        <v>72.75669860839844</v>
       </c>
       <c r="C111" t="n">
         <v>109.6600036621094</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>71.63657379150391</v>
+        <v>71.63658905029297</v>
       </c>
       <c r="C112" t="n">
         <v>107.1100006103516</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>73.36209869384766</v>
+        <v>73.36212921142578</v>
       </c>
       <c r="C113" t="n">
         <v>109.6900024414062</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>72.80698394775391</v>
+        <v>72.8070068359375</v>
       </c>
       <c r="C114" t="n">
         <v>108.8600006103516</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>71.45438385009766</v>
+        <v>71.45436859130859</v>
       </c>
       <c r="C115" t="n">
         <v>105.9700012207031</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>77.52294158935547</v>
+        <v>77.52297210693359</v>
       </c>
       <c r="C116" t="n">
         <v>114.9700012207031</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>74.15168762207031</v>
+        <v>74.15167999267578</v>
       </c>
       <c r="C118" t="n">
         <v>109.0400009155273</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>81.40776062011719</v>
+        <v>81.40771484375</v>
       </c>
       <c r="C119" t="n">
         <v>119.7099990844727</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>81.02689361572266</v>
+        <v>81.02692413330078</v>
       </c>
       <c r="C120" t="n">
         <v>119.1500015258789</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>87.2027587890625</v>
+        <v>87.20275115966797</v>
       </c>
       <c r="C121" t="n">
         <v>127.3000030517578</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>87.96997833251953</v>
+        <v>87.969970703125</v>
       </c>
       <c r="C122" t="n">
         <v>128.4199981689453</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>92.79020690917969</v>
+        <v>92.79022979736328</v>
       </c>
       <c r="C124" t="n">
         <v>134.5099945068359</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>87.63713073730469</v>
+        <v>87.63710784912109</v>
       </c>
       <c r="C126" t="n">
         <v>127.0400009155273</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>95.51396942138672</v>
+        <v>95.51394653320312</v>
       </c>
       <c r="C127" t="n">
         <v>137.4799957275391</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>90.00460052490234</v>
+        <v>90.00463104248047</v>
       </c>
       <c r="C128" t="n">
         <v>129.5500030517578</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>88.96942138671875</v>
+        <v>88.96940612792969</v>
       </c>
       <c r="C129" t="n">
         <v>128.0599975585938</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>80.05592346191406</v>
+        <v>80.05591583251953</v>
       </c>
       <c r="C131" t="n">
         <v>114.4100036621094</v>
@@ -3766,7 +3766,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>80.89556121826172</v>
+        <v>80.89561462402344</v>
       </c>
       <c r="C132" t="n">
         <v>115.6100006103516</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>80.50042724609375</v>
+        <v>80.50043487548828</v>
       </c>
       <c r="C133" t="n">
         <v>114.120002746582</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>85.44530487060547</v>
+        <v>85.44526672363281</v>
       </c>
       <c r="C134" t="n">
         <v>121.129997253418</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>93.50098419189453</v>
+        <v>93.50096130371094</v>
       </c>
       <c r="C135" t="n">
         <v>132.5500030517578</v>
@@ -3882,7 +3882,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>93.53223419189453</v>
+        <v>93.53220367431641</v>
       </c>
       <c r="C136" t="n">
         <v>131.6300048828125</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>92.18210601806641</v>
+        <v>92.18212890625</v>
       </c>
       <c r="C138" t="n">
         <v>129.7299957275391</v>
@@ -3969,7 +3969,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>92.42616271972656</v>
+        <v>92.42617797851562</v>
       </c>
       <c r="C139" t="n">
         <v>129.1100006103516</v>
@@ -3998,7 +3998,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>88.16674041748047</v>
+        <v>88.16670989990234</v>
       </c>
       <c r="C140" t="n">
         <v>123.1600036621094</v>
@@ -4027,7 +4027,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>88.25980377197266</v>
+        <v>88.25978088378906</v>
       </c>
       <c r="C141" t="n">
         <v>123.2900009155273</v>
@@ -4056,7 +4056,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>84.92849731445312</v>
+        <v>84.92848968505859</v>
       </c>
       <c r="C142" t="n">
         <v>117.6800003051758</v>
@@ -4085,7 +4085,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>81.19735717773438</v>
+        <v>81.19734191894531</v>
       </c>
       <c r="C143" t="n">
         <v>112.5100021362305</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>86.42959594726562</v>
+        <v>86.42961120605469</v>
       </c>
       <c r="C144" t="n">
         <v>119.7600021362305</v>
@@ -4172,7 +4172,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>85.11356353759766</v>
+        <v>85.11357879638672</v>
       </c>
       <c r="C146" t="n">
         <v>117</v>
@@ -4201,7 +4201,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>80.69058227539062</v>
+        <v>80.69057464599609</v>
       </c>
       <c r="C147" t="n">
         <v>110.9199981689453</v>
@@ -4259,7 +4259,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>76.00193786621094</v>
+        <v>76.00194549560547</v>
       </c>
       <c r="C149" t="n">
         <v>103.5400009155273</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>74.02735900878906</v>
+        <v>74.02736663818359</v>
       </c>
       <c r="C150" t="n">
         <v>100.8499984741211</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>78.09835052490234</v>
+        <v>78.09835815429688</v>
       </c>
       <c r="C151" t="n">
         <v>105.3399963378906</v>
@@ -4346,7 +4346,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>84.41502380371094</v>
+        <v>84.41504669189453</v>
       </c>
       <c r="C152" t="n">
         <v>113.8600006103516</v>
@@ -4375,7 +4375,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>85.66055297851562</v>
+        <v>85.66056060791016</v>
       </c>
       <c r="C153" t="n">
         <v>115.5400009155273</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>84.98018646240234</v>
+        <v>84.98017883300781</v>
       </c>
       <c r="C154" t="n">
         <v>113.6399993896484</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>77.99570465087891</v>
+        <v>77.99571228027344</v>
       </c>
       <c r="C155" t="n">
         <v>104.3000030517578</v>
@@ -4462,7 +4462,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>86.27386474609375</v>
+        <v>86.27385711669922</v>
       </c>
       <c r="C156" t="n">
         <v>115.370002746582</v>
@@ -4491,7 +4491,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>85.96858978271484</v>
+        <v>85.96862030029297</v>
       </c>
       <c r="C157" t="n">
         <v>113.9400024414062</v>
@@ -4520,7 +4520,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>84.03707122802734</v>
+        <v>84.03708648681641</v>
       </c>
       <c r="C158" t="n">
         <v>111.379997253418</v>
@@ -4578,7 +4578,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>94.320068359375</v>
+        <v>94.32008361816406</v>
       </c>
       <c r="C160" t="n">
         <v>123.9000015258789</v>
@@ -4607,7 +4607,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>97.73050689697266</v>
+        <v>97.73052215576172</v>
       </c>
       <c r="C161" t="n">
         <v>128.3800048828125</v>
@@ -4636,7 +4636,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>97.35749053955078</v>
+        <v>97.35749816894531</v>
       </c>
       <c r="C162" t="n">
         <v>127.8899993896484</v>
@@ -4665,7 +4665,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>102.2495651245117</v>
+        <v>102.2495880126953</v>
       </c>
       <c r="C163" t="n">
         <v>133.2799987792969</v>
@@ -4723,7 +4723,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>108.256591796875</v>
+        <v>108.2566070556641</v>
       </c>
       <c r="C165" t="n">
         <v>141.1100006103516</v>
@@ -4752,7 +4752,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>109.7701644897461</v>
+        <v>109.7701263427734</v>
       </c>
       <c r="C166" t="n">
         <v>142.0500030517578</v>
@@ -4781,7 +4781,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>102.6839599609375</v>
+        <v>102.6839904785156</v>
       </c>
       <c r="C167" t="n">
         <v>132.8800048828125</v>
@@ -4810,7 +4810,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>105.3577194213867</v>
+        <v>105.3576965332031</v>
       </c>
       <c r="C168" t="n">
         <v>136.3399963378906</v>
@@ -4839,7 +4839,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>107.0950164794922</v>
+        <v>107.0950469970703</v>
       </c>
       <c r="C169" t="n">
         <v>137.5500030517578</v>
@@ -4868,7 +4868,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>111.5252304077148</v>
+        <v>111.5251922607422</v>
       </c>
       <c r="C170" t="n">
         <v>143.2400054931641</v>
@@ -4897,7 +4897,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>102.1432418823242</v>
+        <v>102.1432266235352</v>
       </c>
       <c r="C171" t="n">
         <v>131.1900024414062</v>
@@ -4926,7 +4926,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>100.2820892333984</v>
+        <v>100.2821044921875</v>
       </c>
       <c r="C172" t="n">
         <v>127.870002746582</v>
@@ -4955,7 +4955,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>108.6029586791992</v>
+        <v>108.6029815673828</v>
       </c>
       <c r="C173" t="n">
         <v>138.4799957275391</v>
@@ -4984,7 +4984,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>110.9243774414062</v>
+        <v>110.9243469238281</v>
       </c>
       <c r="C174" t="n">
         <v>141.4400024414062</v>
@@ -5013,7 +5013,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>111.6974792480469</v>
+        <v>111.6974639892578</v>
       </c>
       <c r="C175" t="n">
         <v>141.3500061035156</v>
@@ -5042,7 +5042,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>120.144889831543</v>
+        <v>120.1448822021484</v>
       </c>
       <c r="C176" t="n">
         <v>152.0399932861328</v>
@@ -5071,7 +5071,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>124.6649398803711</v>
+        <v>124.6649780273438</v>
       </c>
       <c r="C177" t="n">
         <v>157.7599945068359</v>
@@ -5100,7 +5100,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>117.4869384765625</v>
+        <v>117.4869232177734</v>
       </c>
       <c r="C178" t="n">
         <v>147.6600036621094</v>
@@ -5158,7 +5158,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>110.8432235717773</v>
+        <v>110.8432312011719</v>
       </c>
       <c r="C180" t="n">
         <v>139.3099975585938</v>
@@ -5187,7 +5187,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>108.1149139404297</v>
+        <v>108.1148834228516</v>
       </c>
       <c r="C181" t="n">
         <v>134.8300018310547</v>
@@ -5216,7 +5216,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>105.9257965087891</v>
+        <v>105.9258117675781</v>
       </c>
       <c r="C182" t="n">
         <v>132.1000061035156</v>
@@ -5245,7 +5245,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>102.9028015136719</v>
+        <v>102.9027862548828</v>
       </c>
       <c r="C183" t="n">
         <v>128.3300018310547</v>
@@ -5274,7 +5274,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>112.4810943603516</v>
+        <v>112.4811019897461</v>
       </c>
       <c r="C184" t="n">
         <v>139.0500030517578</v>
@@ -5303,7 +5303,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>107.8459854125977</v>
+        <v>107.8459625244141</v>
       </c>
       <c r="C185" t="n">
         <v>133.3200073242188</v>
@@ -5390,7 +5390,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>110.7531280517578</v>
+        <v>110.7531051635742</v>
       </c>
       <c r="C188" t="n">
         <v>135.7200012207031</v>
@@ -5419,7 +5419,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>112.4586486816406</v>
+        <v>112.458625793457</v>
       </c>
       <c r="C189" t="n">
         <v>137.8099975585938</v>
@@ -5448,7 +5448,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>108.9543609619141</v>
+        <v>108.9543533325195</v>
       </c>
       <c r="C190" t="n">
         <v>132.4400024414062</v>
@@ -5506,7 +5506,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>107.2020645141602</v>
+        <v>107.2020721435547</v>
       </c>
       <c r="C192" t="n">
         <v>130.3099975585938</v>
@@ -5535,7 +5535,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>118.5632858276367</v>
+        <v>118.5633316040039</v>
       </c>
       <c r="C193" t="n">
         <v>142.9199981689453</v>
@@ -5564,7 +5564,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>114.1914215087891</v>
+        <v>114.1913909912109</v>
       </c>
       <c r="C194" t="n">
         <v>137.6499938964844</v>
@@ -5593,7 +5593,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>107.9696044921875</v>
+        <v>107.9695816040039</v>
       </c>
       <c r="C195" t="n">
         <v>130.1499938964844</v>
@@ -5622,7 +5622,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>103.0920104980469</v>
+        <v>103.0920181274414</v>
       </c>
       <c r="C196" t="n">
         <v>123.1600036621094</v>
@@ -5680,7 +5680,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>111.3454055786133</v>
+        <v>111.3454208374023</v>
       </c>
       <c r="C198" t="n">
         <v>133.0200042724609</v>
@@ -5709,7 +5709,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>114.1404876708984</v>
+        <v>114.140495300293</v>
       </c>
       <c r="C199" t="n">
         <v>135.1499938964844</v>
@@ -5738,7 +5738,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>111.3028259277344</v>
+        <v>111.3028335571289</v>
       </c>
       <c r="C200" t="n">
         <v>131.7899932861328</v>
@@ -5767,7 +5767,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>107.6966323852539</v>
+        <v>107.6966171264648</v>
       </c>
       <c r="C201" t="n">
         <v>127.5199966430664</v>
@@ -5854,7 +5854,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>115.5981216430664</v>
+        <v>115.5980987548828</v>
       </c>
       <c r="C204" t="n">
         <v>135.6300048828125</v>
@@ -5883,7 +5883,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>116.6905822753906</v>
+        <v>116.6905975341797</v>
       </c>
       <c r="C205" t="n">
         <v>135.75</v>
@@ -5912,7 +5912,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>111.756477355957</v>
+        <v>111.7564926147461</v>
       </c>
       <c r="C206" t="n">
         <v>130.0099945068359</v>
@@ -5941,7 +5941,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>107.4929046630859</v>
+        <v>107.4928817749023</v>
       </c>
       <c r="C207" t="n">
         <v>125.0500030517578</v>
@@ -5970,7 +5970,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>116.485710144043</v>
+        <v>116.4856796264648</v>
       </c>
       <c r="C208" t="n">
         <v>134.2200012207031</v>
@@ -5999,7 +5999,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>125.7458724975586</v>
+        <v>125.7458877563477</v>
       </c>
       <c r="C209" t="n">
         <v>144.8899993896484</v>
@@ -6028,7 +6028,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>116.5377655029297</v>
+        <v>116.5377578735352</v>
       </c>
       <c r="C210" t="n">
         <v>134.2799987792969</v>
@@ -6057,7 +6057,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>120.8748321533203</v>
+        <v>120.8748550415039</v>
       </c>
       <c r="C211" t="n">
         <v>138.0599975585938</v>
@@ -6086,7 +6086,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>113.0301666259766</v>
+        <v>113.030158996582</v>
       </c>
       <c r="C212" t="n">
         <v>129.1000061035156</v>
@@ -6115,7 +6115,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>112.7937469482422</v>
+        <v>112.7937545776367</v>
       </c>
       <c r="C213" t="n">
         <v>128.8300018310547</v>
@@ -6144,7 +6144,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>106.8026351928711</v>
+        <v>106.8026428222656</v>
       </c>
       <c r="C214" t="n">
         <v>120.8499984741211</v>
@@ -6173,7 +6173,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>105.733283996582</v>
+        <v>105.7332763671875</v>
       </c>
       <c r="C215" t="n">
         <v>119.6399993896484</v>
@@ -6202,7 +6202,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>109.3478698730469</v>
+        <v>109.3478775024414</v>
       </c>
       <c r="C216" t="n">
         <v>123.7300033569336</v>
@@ -6231,7 +6231,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>108.4308242797852</v>
+        <v>108.4308166503906</v>
       </c>
       <c r="C217" t="n">
         <v>121.5100021362305</v>
@@ -6260,7 +6260,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>107.9489517211914</v>
+        <v>107.9489440917969</v>
       </c>
       <c r="C218" t="n">
         <v>120.9700012207031</v>
@@ -6289,7 +6289,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>108.1274185180664</v>
+        <v>108.1274108886719</v>
       </c>
       <c r="C219" t="n">
         <v>121.1699981689453</v>
@@ -6318,7 +6318,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>116.5663528442383</v>
+        <v>116.5663604736328</v>
       </c>
       <c r="C220" t="n">
         <v>129.3500061035156</v>
@@ -6376,7 +6376,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>120.1259536743164</v>
+        <v>120.1259765625</v>
       </c>
       <c r="C222" t="n">
         <v>133.3000030517578</v>
@@ -6434,7 +6434,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>122.7965316772461</v>
+        <v>122.7965545654297</v>
       </c>
       <c r="C224" t="n">
         <v>135.0500030517578</v>
@@ -6463,7 +6463,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>131.5346069335938</v>
+        <v>131.5345916748047</v>
       </c>
       <c r="C225" t="n">
         <v>144.6600036621094</v>
@@ -6492,7 +6492,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>130.4454956054688</v>
+        <v>130.4454650878906</v>
       </c>
       <c r="C226" t="n">
         <v>142.2799987792969</v>
@@ -6521,7 +6521,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>123.0192108154297</v>
+        <v>123.0191955566406</v>
       </c>
       <c r="C227" t="n">
         <v>134.1799926757812</v>
@@ -6579,7 +6579,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>121.2107925415039</v>
+        <v>121.2107849121094</v>
       </c>
       <c r="C229" t="n">
         <v>131.0399932861328</v>
@@ -6608,7 +6608,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>120.2210693359375</v>
+        <v>120.2210540771484</v>
       </c>
       <c r="C230" t="n">
         <v>129.9700012207031</v>
@@ -6637,7 +6637,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>131.3579559326172</v>
+        <v>131.3579406738281</v>
       </c>
       <c r="C231" t="n">
         <v>142.0099945068359</v>
@@ -6695,7 +6695,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>122.9834136962891</v>
+        <v>122.9834060668945</v>
       </c>
       <c r="C233" t="n">
         <v>131.7799987792969</v>
@@ -6724,7 +6724,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>134.1637268066406</v>
+        <v>134.1637115478516</v>
       </c>
       <c r="C234" t="n">
         <v>143.7599945068359</v>
@@ -6753,7 +6753,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>121.4453048706055</v>
+        <v>121.4452972412109</v>
       </c>
       <c r="C235" t="n">
         <v>128.9199981689453</v>
@@ -6898,7 +6898,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>103.8058776855469</v>
+        <v>103.8058853149414</v>
       </c>
       <c r="C240" t="n">
         <v>109.120002746582</v>
@@ -7014,7 +7014,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>94.03452301025391</v>
+        <v>94.03453063964844</v>
       </c>
       <c r="C244" t="n">
         <v>96.47000122070312</v>
@@ -7043,7 +7043,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>95.94503784179688</v>
+        <v>95.94504547119141</v>
       </c>
       <c r="C245" t="n">
         <v>98.43000030517578</v>
